--- a/sinodalias.xlsx
+++ b/sinodalias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B659A0-A6E4-C444-AF49-82CB0E21A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDD3BF1-E0B0-6F4C-8457-5A329AF5E5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="25600" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurado" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="165">
   <si>
     <t>FUNCIÓN</t>
   </si>
@@ -506,6 +506,15 @@
   </si>
   <si>
     <t>DIAGNÓSTICO DE FALLAS BASADO EN MODELOS QLPV PARA UN VANT TIPO QUADROTOR</t>
+  </si>
+  <si>
+    <t>JUAN ENRIQUE COUTIÑO RUIZ</t>
+  </si>
+  <si>
+    <t>26/02/2013</t>
+  </si>
+  <si>
+    <t>ERNESTO VELAZQUEZ CRUZ</t>
   </si>
 </sst>
 </file>
@@ -730,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -2730,6 +2739,40 @@
         <v>161</v>
       </c>
     </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>162</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>164</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D117" t="s">
+        <v>7</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F113">
     <sortCondition ref="B2:B113"/>
